--- a/healthcare_assessment_forms/011_epiglottitis_knowledge_assessment--healthcare_assessment_forms.xlsx
+++ b/healthcare_assessment_forms/011_epiglottitis_knowledge_assessment--healthcare_assessment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>form_header</t>
+          <t>question_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Form Header</t>
+          <t>Definition of Epiglottitis</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,225 +543,225 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>question_1</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>What is Epiglottitis?</t>
+          <t>Symptoms of Epiglottitis</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>question_1_confidence_level</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Next Course of Action</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>question_2</t>
+          <t>question_4_confidence_level_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What are the symptoms?</t>
+          <t>Confidence Level</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question_2_confidence_level</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Complications of Epiglottitis</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question_3</t>
+          <t>question_5_confidence_level_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is the next step?</t>
+          <t>Question 5 Confidence Level 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>question_3_confidence_level</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Treatment Options for Epiglottitis</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_6_confidence_level_3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>What are the complications?</t>
+          <t>Question 6 Confidence Level 3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>question_4_confidence_level</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Referral Guidelines</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_7_confidence_level_4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>When to Refer?</t>
+          <t>Question 7 Confidence Level 4</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>question_5_confidence_level</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Confidence Level</t>
+          <t>Patient Education</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Form Footer</t>
+          <t>Form Conclusion</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -799,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="8" customWidth="1" min="3" max="3"/>
   </cols>
@@ -827,7 +827,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>question_1_confidence_level_choices</t>
+          <t>question_4_confidence_level_1_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -844,7 +844,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>question_1_confidence_level_choices</t>
+          <t>question_4_confidence_level_1_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>question_1_confidence_level_choices</t>
+          <t>question_4_confidence_level_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -878,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>question_2_confidence_level_choices</t>
+          <t>question_5_confidence_level_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>question_2_confidence_level_choices</t>
+          <t>question_5_confidence_level_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -912,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>question_2_confidence_level_choices</t>
+          <t>question_5_confidence_level_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -929,7 +929,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>question_3_confidence_level_choices</t>
+          <t>question_6_confidence_level_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>question_3_confidence_level_choices</t>
+          <t>question_6_confidence_level_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -963,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>question_3_confidence_level_choices</t>
+          <t>question_6_confidence_level_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -980,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_4_confidence_level_choices</t>
+          <t>question_7_confidence_level_4_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -997,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_4_confidence_level_choices</t>
+          <t>question_7_confidence_level_4_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1014,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_4_confidence_level_choices</t>
+          <t>question_7_confidence_level_4_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1023,57 +1023,6 @@
         </is>
       </c>
       <c r="C13" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>question_5_confidence_level_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>question_5_confidence_level_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>question_5_confidence_level_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
